--- a/ig/DM-SEPTEMBRE-2026/ValueSet-jdv-evolution-cisis.xlsx
+++ b/ig/DM-SEPTEMBRE-2026/ValueSet-jdv-evolution-cisis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="46">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260716085852</t>
+    <t>20260911143444</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T08:58:52+01:00</t>
+    <t>2026-09-11T14:34:44+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -100,12 +100,6 @@
     <t>Concept</t>
   </si>
   <si>
-    <t>MED-1281</t>
-  </si>
-  <si>
-    <t>décès auquel l’effet a pu contribuer</t>
-  </si>
-  <si>
     <t>MED-1282</t>
   </si>
   <si>
@@ -121,6 +115,18 @@
     <t>https://smt.esante.gouv.fr/fhir/CodeSystem/terminologie-cisis</t>
   </si>
   <si>
+    <t>1336140009</t>
+  </si>
+  <si>
+    <t>en cours de guérison de l'évènement indésirable</t>
+  </si>
+  <si>
+    <t>1339036001</t>
+  </si>
+  <si>
+    <t>évènement indésirable persistant sans guérison</t>
+  </si>
+  <si>
     <t>1352007006</t>
   </si>
   <si>
@@ -131,18 +137,6 @@
   </si>
   <si>
     <t>guéri(e) de l’évènement indésirable avec séquelle</t>
-  </si>
-  <si>
-    <t>1336140009</t>
-  </si>
-  <si>
-    <t>en cours de guérison de l'évènement indésirable</t>
-  </si>
-  <si>
-    <t>1339036001</t>
-  </si>
-  <si>
-    <t>évènement indésirable persistant sans guérison</t>
   </si>
   <si>
     <t>405535005</t>
@@ -421,7 +415,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -449,23 +443,15 @@
         <v>30</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s" s="2">
         <v>32</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -492,66 +478,66 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM-SEPTEMBRE-2026/ValueSet-jdv-evolution-cisis.xlsx
+++ b/ig/DM-SEPTEMBRE-2026/ValueSet-jdv-evolution-cisis.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260911143444</t>
+    <t>20260916095454</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T14:34:44+01:00</t>
+    <t>2026-09-16T09:54:54+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
